--- a/Modulos Curso/Modulo 3/7 Pasos/3 y 4. Costos y Adquisiciones.xlsx
+++ b/Modulos Curso/Modulo 3/7 Pasos/3 y 4. Costos y Adquisiciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UNAL\2026-1S (XII)\Automatizacion de Procesos de Manufactura\imagnes web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430DF142-61C0-4BD3-B832-0B6F38F86673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC147D24-8F1D-4C38-84E1-225CC297379E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="2" xr2:uid="{EA908970-9E33-4CDE-A21B-95580596BCC2}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="289">
   <si>
     <t>Categoría</t>
   </si>
@@ -762,9 +762,6 @@
     <t>MLT TOTAL</t>
   </si>
   <si>
-    <t>Eficiencia</t>
-  </si>
-  <si>
     <t>Disponibilidad</t>
   </si>
   <si>
@@ -900,13 +897,19 @@
     <t>Capacitación y documentación</t>
   </si>
   <si>
-    <t>compra de equipos</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
     <t>Planeación</t>
+  </si>
+  <si>
+    <t>OEE</t>
+  </si>
+  <si>
+    <t>Rendimiento</t>
+  </si>
+  <si>
+    <t>Compra de equipos</t>
   </si>
 </sst>
 </file>
@@ -917,9 +920,9 @@
     <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="175" formatCode="0.000"/>
-    <numFmt numFmtId="182" formatCode="0.000000000"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.000000000"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -1275,7 +1278,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1314,12 +1317,6 @@
     <xf numFmtId="6" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="8" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -1346,18 +1343,6 @@
     </xf>
     <xf numFmtId="6" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1441,159 +1426,180 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="6" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="6" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="6" fontId="6" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="6" fontId="6" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="6" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="3" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="6" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="6" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1718,61 +1724,61 @@
                   <c:v>-912716600</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-912716600</c:v>
+                  <c:v>16449190.441324234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1806,61 +1812,61 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1121238047.5383224</c:v>
+                  <c:v>188949190.44132423</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1894,61 +1900,61 @@
                   <c:v>-912716600</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>208521447.53832245</c:v>
+                  <c:v>205398380.88264847</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1982,61 +1988,61 @@
                   <c:v>-912716600</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-704195152.46167755</c:v>
+                  <c:v>-707318219.11735153</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-495673704.9233551</c:v>
+                  <c:v>-501919838.23470306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-287152257.38503265</c:v>
+                  <c:v>-296521457.3520546</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-78630809.846710205</c:v>
+                  <c:v>-91123076.469406128</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>129890637.69161224</c:v>
+                  <c:v>114275304.41324234</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>338412085.22993469</c:v>
+                  <c:v>319673685.29589081</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>546933532.76825714</c:v>
+                  <c:v>525072066.17853928</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>755454980.30657959</c:v>
+                  <c:v>730470447.06118774</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>963976427.84490204</c:v>
+                  <c:v>935868827.94383621</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1172497875.3832245</c:v>
+                  <c:v>1141267208.8264847</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1381019322.9215469</c:v>
+                  <c:v>1346665589.7091331</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1589540770.4598694</c:v>
+                  <c:v>1552063970.5917816</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1798062217.9981918</c:v>
+                  <c:v>1757462351.4744301</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2006583665.5365143</c:v>
+                  <c:v>1962860732.3570786</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2215105113.0748367</c:v>
+                  <c:v>2168259113.239727</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2423626560.6131592</c:v>
+                  <c:v>2373657494.1223755</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2632148008.1514816</c:v>
+                  <c:v>2579055875.005024</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2840669455.6898041</c:v>
+                  <c:v>2784454255.8876724</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3049190903.2281265</c:v>
+                  <c:v>2989852636.7703209</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5024,14 +5030,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="89" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="D1" s="27" t="s">
+      <c r="B1" s="90"/>
+      <c r="D1" s="85" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="28"/>
+      <c r="E1" s="86"/>
     </row>
     <row r="2" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
@@ -5040,10 +5046,10 @@
       <c r="B2" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="21" t="s">
         <v>123</v>
       </c>
     </row>
@@ -5054,22 +5060,22 @@
       <c r="B3" s="15">
         <v>-5000000</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="E3" s="25">
+      <c r="E3" s="23">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B4" s="15">
         <v>-12000000</v>
       </c>
-      <c r="D4" s="24"/>
-      <c r="E4" s="25"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="23"/>
     </row>
     <row r="5" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
@@ -5079,10 +5085,10 @@
         <f>-1*E8</f>
         <v>-32400000</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="23">
         <v>16</v>
       </c>
     </row>
@@ -5094,10 +5100,10 @@
         <f>-1*(Adquisiciones!E31+Adquisiciones!E32+Adquisiciones!E33)</f>
         <v>-37500000</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="23">
         <v>300</v>
       </c>
     </row>
@@ -5109,10 +5115,10 @@
         <f>-1*(Adquisiciones!F28)</f>
         <v>-22100000</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="24">
         <v>750</v>
       </c>
     </row>
@@ -5143,7 +5149,7 @@
     </row>
     <row r="10" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B10" s="15">
         <v>-8000000</v>
@@ -5160,14 +5166,14 @@
     </row>
     <row r="12" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="13" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="89" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="D13" s="27" t="s">
+      <c r="B13" s="90"/>
+      <c r="D13" s="85" t="s">
         <v>128</v>
       </c>
-      <c r="E13" s="28"/>
+      <c r="E13" s="86"/>
     </row>
     <row r="14" spans="1:5" ht="27.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
@@ -5176,10 +5182,10 @@
       <c r="B14" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="21" t="s">
         <v>103</v>
       </c>
     </row>
@@ -5187,7 +5193,7 @@
       <c r="A15" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="18">
         <f>-1*Adquisiciones!F36-SUM(B6:B9)</f>
         <v>-636100000</v>
       </c>
@@ -5202,7 +5208,7 @@
       <c r="A16" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="19">
         <f>0.1*B15</f>
         <v>-63610000</v>
       </c>
@@ -5243,9 +5249,9 @@
     </row>
     <row r="19" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="B19" s="21">
+        <v>255</v>
+      </c>
+      <c r="B19" s="19">
         <v>20000000</v>
       </c>
       <c r="D19" s="13"/>
@@ -5270,7 +5276,7 @@
       <c r="A21" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="16">
         <f>SUM(B15:B20)</f>
         <v>-740216600</v>
       </c>
@@ -5283,18 +5289,18 @@
     </row>
     <row r="22" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="23" spans="1:8" ht="26.4" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="89" t="s">
         <v>134</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="D23" s="29" t="s">
+      <c r="B23" s="90"/>
+      <c r="D23" s="91" t="s">
         <v>138</v>
       </c>
-      <c r="E23" s="30"/>
-      <c r="G23" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="H23" s="30"/>
+      <c r="E23" s="92"/>
+      <c r="G23" s="91" t="s">
+        <v>248</v>
+      </c>
+      <c r="H23" s="92"/>
     </row>
     <row r="24" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
@@ -5303,16 +5309,16 @@
       <c r="B24" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="G24" s="22" t="s">
+      <c r="G24" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H24" s="23" t="s">
+      <c r="H24" s="21" t="s">
         <v>139</v>
       </c>
     </row>
@@ -5331,9 +5337,9 @@
         <v>15191856</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="H25" s="78">
+        <v>249</v>
+      </c>
+      <c r="H25" s="55">
         <v>1500</v>
       </c>
     </row>
@@ -5341,18 +5347,18 @@
       <c r="A26" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="B26" s="109">
+      <c r="B26" s="83">
         <f>Producción!J59</f>
-        <v>1058004883.5383224</v>
+        <v>125716026.44132423</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="17">
         <v>2</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H26" s="15">
         <v>2466</v>
@@ -5369,13 +5375,13 @@
       <c r="D27" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="17">
         <v>2</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="H27" s="19">
+        <v>251</v>
+      </c>
+      <c r="H27" s="17">
         <v>2</v>
       </c>
     </row>
@@ -5385,7 +5391,7 @@
       </c>
       <c r="B28" s="15">
         <f>SUM(B25:B27)</f>
-        <v>1121238047.5383224</v>
+        <v>188949190.44132423</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>100</v>
@@ -5394,9 +5400,9 @@
         <v>60767424</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="H28" s="35">
+        <v>252</v>
+      </c>
+      <c r="H28" s="29">
         <v>0.33</v>
       </c>
     </row>
@@ -5433,21 +5439,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="96" t="s">
         <v>143</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="63" t="s">
+      <c r="B1" s="97"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="96" t="s">
         <v>144</v>
       </c>
-      <c r="E1" s="64"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
     </row>
     <row r="2" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
@@ -5456,145 +5462,146 @@
       <c r="B2" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="32"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="12" t="s">
         <v>146</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
     </row>
     <row r="3" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="17">
         <v>1</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="33" t="s">
+      <c r="C3" s="26"/>
+      <c r="D3" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="E3" s="101">
+      <c r="E3" s="76">
         <v>2</v>
       </c>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
     </row>
     <row r="4" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="17">
         <v>10</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="33" t="s">
+      <c r="C4" s="26"/>
+      <c r="D4" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="E4" s="102">
+      <c r="E4" s="77">
         <v>1.75</v>
       </c>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
     </row>
     <row r="5" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="B5" s="19">
-        <v>20000</v>
-      </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="33" t="s">
+      <c r="B5" s="17">
+        <f>ROUND((D50/D43),0)</f>
+        <v>1685</v>
+      </c>
+      <c r="C5" s="26"/>
+      <c r="D5" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="E5" s="102">
+      <c r="E5" s="77">
         <v>1.5</v>
       </c>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="17">
         <v>2</v>
       </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="17">
         <v>8</v>
       </c>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="34"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
+      <c r="A8" s="28"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="89" t="s">
         <v>155</v>
       </c>
-      <c r="B9" s="65"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="32"/>
+      <c r="B9" s="103"/>
+      <c r="C9" s="90"/>
+      <c r="D9" s="26"/>
       <c r="E9" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="F9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
+      <c r="F9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
@@ -5606,423 +5613,424 @@
       <c r="C10" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="19">
+      <c r="D10" s="26"/>
+      <c r="E10" s="17">
         <f>B6*B7</f>
         <v>16</v>
       </c>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="17">
+        <f>352300000</f>
         <v>352300000</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="29">
         <v>1</v>
       </c>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="17">
         <f>B11*C12</f>
         <v>267748000</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="29">
         <v>0.76</v>
       </c>
-      <c r="D12" s="32"/>
+      <c r="D12" s="26"/>
       <c r="E12" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="B13" s="99">
+      <c r="B13" s="74">
         <f>B12*C13</f>
         <v>187423600</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="29">
         <v>0.7</v>
       </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="35">
+      <c r="D13" s="26"/>
+      <c r="E13" s="29">
         <v>0.02</v>
       </c>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
     </row>
     <row r="14" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="17">
         <f>ROUNDUP(B13*C14,0)</f>
         <v>513490</v>
       </c>
-      <c r="C14" s="98">
+      <c r="C14" s="73">
         <f>1/365</f>
         <v>2.7397260273972603E-3</v>
       </c>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
     </row>
     <row r="15" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="89" t="s">
         <v>163</v>
       </c>
-      <c r="B15" s="65"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
+      <c r="B15" s="103"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
     </row>
     <row r="16" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="17">
         <f>ROUNDUP(B14*C16,0)</f>
         <v>256745</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="29">
         <v>0.5</v>
       </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
     </row>
     <row r="17" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="17">
         <f>ROUNDUP(B14*C17,0)</f>
         <v>15405</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="29">
         <v>0.03</v>
       </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
     </row>
     <row r="18" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="17">
         <f>ROUNDUP(B14*C18,0)</f>
         <v>15405</v>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="29">
         <v>0.03</v>
       </c>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
     </row>
     <row r="19" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="89" t="s">
         <v>167</v>
       </c>
-      <c r="B19" s="65"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="32"/>
+      <c r="B19" s="103"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="26"/>
       <c r="E19" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
     </row>
     <row r="20" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="17">
         <f>ROUNDUP(B16*$E$20*$E$22*C20,0)</f>
         <v>728914</v>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="29">
         <v>0.5</v>
       </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="19">
+      <c r="D20" s="26"/>
+      <c r="E20" s="17">
         <f>24*8</f>
         <v>192</v>
       </c>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
     </row>
     <row r="21" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="17">
         <f>ROUNDUP(B17*$E$20*$E$22*C21,0)</f>
         <v>43736</v>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="29">
         <v>0.5</v>
       </c>
-      <c r="D21" s="32"/>
+      <c r="D21" s="26"/>
       <c r="E21" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
     </row>
     <row r="22" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="17">
         <f>ROUNDUP(B18*$E$20*$E$22*C22,0)</f>
         <v>43736</v>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="29">
         <v>0.5</v>
       </c>
-      <c r="D22" s="32"/>
-      <c r="E22" s="19">
+      <c r="D22" s="26"/>
+      <c r="E22" s="17">
         <f>29.5735/1000</f>
         <v>2.9573499999999999E-2</v>
       </c>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="26"/>
     </row>
     <row r="23" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="89" t="s">
         <v>173</v>
       </c>
-      <c r="B23" s="65"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
+      <c r="B23" s="103"/>
+      <c r="C23" s="90"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
     </row>
     <row r="24" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="17">
         <f>ROUNDUP(B20/E3,0)</f>
         <v>364457</v>
       </c>
-      <c r="C24" s="37">
+      <c r="C24" s="31">
         <v>0.87060000000000004</v>
       </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
     </row>
     <row r="25" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="17">
         <f>ROUNDUP(B21/E4,0)</f>
         <v>24992</v>
       </c>
-      <c r="C25" s="37">
+      <c r="C25" s="31">
         <v>5.9700000000000003E-2</v>
       </c>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
     </row>
     <row r="26" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="17">
         <f>ROUNDUP(B22/E5,0)</f>
         <v>29158</v>
       </c>
-      <c r="C26" s="37">
+      <c r="C26" s="31">
         <v>6.9699999999999998E-2</v>
       </c>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="66" t="s">
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="98" t="s">
         <v>177</v>
       </c>
-      <c r="H26" s="67"/>
-      <c r="I26" s="68"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="38"/>
-      <c r="M26" s="29" t="s">
-        <v>268</v>
-      </c>
-      <c r="N26" s="30"/>
+      <c r="H26" s="99"/>
+      <c r="I26" s="100"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="M26" s="91" t="s">
+        <v>267</v>
+      </c>
+      <c r="N26" s="92"/>
     </row>
     <row r="27" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="B27" s="69">
+      <c r="B27" s="101">
         <f>SUM(B24:B26)</f>
         <v>418607</v>
       </c>
-      <c r="C27" s="70"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="39" t="s">
+      <c r="C27" s="102"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="H27" s="40" t="s">
+      <c r="H27" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="I27" s="41" t="s">
+      <c r="I27" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="J27" s="42"/>
-      <c r="K27" s="42"/>
+      <c r="J27" s="36"/>
+      <c r="K27" s="36"/>
       <c r="M27" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="N27" s="19">
+      <c r="N27" s="17">
         <v>4225000000</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="27.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="43"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="45" t="s">
+      <c r="A28" s="37"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="39" t="s">
         <v>181</v>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="17">
         <v>4225000000</v>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="17">
         <f>H28</f>
         <v>4225000000</v>
       </c>
-      <c r="J28" s="42"/>
-      <c r="K28" s="42"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="36"/>
       <c r="M28" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="N28" s="19">
+        <v>268</v>
+      </c>
+      <c r="N28" s="17">
         <v>352300000</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="89" t="s">
         <v>182</v>
       </c>
-      <c r="B29" s="65"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="33" t="s">
+      <c r="B29" s="103"/>
+      <c r="C29" s="90"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="27" t="s">
         <v>183</v>
       </c>
       <c r="H29" s="15">
         <v>13416000000</v>
       </c>
       <c r="I29" s="15">
-        <f>H29*4409.15</f>
+        <f t="shared" ref="I29:I34" si="0">H29*4409.15</f>
         <v>59153156399999.992</v>
       </c>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
       <c r="M29" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="N29" s="37">
+      <c r="N29" s="31">
         <v>8.3400000000000002E-2</v>
       </c>
     </row>
@@ -6036,87 +6044,87 @@
       <c r="C30" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="33" t="s">
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="27" t="s">
         <v>185</v>
       </c>
       <c r="H30" s="15">
         <v>1925000000</v>
       </c>
       <c r="I30" s="15">
-        <f>H30*4409.15</f>
+        <f t="shared" si="0"/>
         <v>8487613749999.999</v>
       </c>
-      <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
-      <c r="M30" s="43"/>
-      <c r="N30" s="44"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="M30" s="37"/>
+      <c r="N30" s="38"/>
     </row>
     <row r="31" spans="1:14" ht="27.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="B31" s="100">
+      <c r="B31" s="75">
         <f>ROUND(B24*($D$50/$B$27),0)</f>
-        <v>182835</v>
+        <v>21766</v>
       </c>
       <c r="C31" s="15">
         <f>B31*$N$35*E3</f>
-        <v>901647145.79999995</v>
-      </c>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="33" t="s">
+        <v>107338593.67999999</v>
+      </c>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="27" t="s">
         <v>186</v>
       </c>
       <c r="H31" s="15">
         <v>1138000000</v>
       </c>
       <c r="I31" s="15">
-        <f>H31*4409.15</f>
+        <f t="shared" si="0"/>
         <v>5017612700000</v>
       </c>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32"/>
-      <c r="M31" s="29" t="s">
-        <v>270</v>
-      </c>
-      <c r="N31" s="30"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+      <c r="M31" s="91" t="s">
+        <v>269</v>
+      </c>
+      <c r="N31" s="92"/>
     </row>
     <row r="32" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="B32" s="100">
+      <c r="B32" s="75">
         <f>ROUND(B25*($D$50/$B$27),0)</f>
-        <v>12538</v>
+        <v>1493</v>
       </c>
       <c r="C32" s="15">
         <f>B32*$N$35*E4</f>
-        <v>54102034.209999993</v>
-      </c>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="33" t="s">
+        <v>6442362.1849999996</v>
+      </c>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="27" t="s">
         <v>187</v>
       </c>
       <c r="H32" s="15">
         <v>14767000000</v>
       </c>
       <c r="I32" s="15">
-        <f>H32*4409.15</f>
+        <f t="shared" si="0"/>
         <v>65109918049999.992</v>
       </c>
-      <c r="J32" s="32"/>
-      <c r="K32" s="32"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
       <c r="M32" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="N32" s="19">
+      <c r="N32" s="17">
         <v>4225000000</v>
       </c>
     </row>
@@ -6124,29 +6132,29 @@
       <c r="A33" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="B33" s="99">
+      <c r="B33" s="74">
         <f>ROUND(B26*($D$50/$B$27),0)</f>
-        <v>14628</v>
+        <v>1741</v>
       </c>
       <c r="C33" s="15">
         <f>B33*$N$35*E5</f>
-        <v>54103267.079999998</v>
-      </c>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="33" t="s">
+        <v>6439280.0099999998</v>
+      </c>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="27" t="s">
         <v>188</v>
       </c>
       <c r="H33" s="15">
         <v>3375000000</v>
       </c>
       <c r="I33" s="15">
-        <f>H33*4409.15</f>
+        <f t="shared" si="0"/>
         <v>14880881249999.998</v>
       </c>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
       <c r="M33" s="13" t="s">
         <v>183</v>
       </c>
@@ -6155,30 +6163,30 @@
       </c>
     </row>
     <row r="34" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="89" t="s">
         <v>189</v>
       </c>
-      <c r="B34" s="65"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="33" t="s">
+      <c r="B34" s="103"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="27" t="s">
         <v>190</v>
       </c>
       <c r="H34" s="15">
         <v>6877000000</v>
       </c>
       <c r="I34" s="15">
-        <f>H34*4409.15</f>
+        <f t="shared" si="0"/>
         <v>30321724549999.996</v>
       </c>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
+      <c r="J34" s="26"/>
+      <c r="K34" s="26"/>
       <c r="M34" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="N34" s="18">
+        <v>270</v>
+      </c>
+      <c r="N34" s="16">
         <v>14000.75</v>
       </c>
     </row>
@@ -6192,10 +6200,10 @@
       <c r="C35" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="33" t="s">
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="27" t="s">
         <v>191</v>
       </c>
       <c r="H35" s="15">
@@ -6205,12 +6213,12 @@
         <f>H36*4409.15</f>
         <v>308.64050000000003</v>
       </c>
-      <c r="J35" s="32"/>
-      <c r="K35" s="32"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="26"/>
       <c r="M35" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="N35" s="18">
+        <v>271</v>
+      </c>
+      <c r="N35" s="16">
         <v>2465.7399999999998</v>
       </c>
     </row>
@@ -6220,28 +6228,28 @@
       </c>
       <c r="B36" s="1">
         <f>C31*C36</f>
-        <v>129386365.42229998</v>
-      </c>
-      <c r="C36" s="37">
+        <v>15403088.193079997</v>
+      </c>
+      <c r="C36" s="31">
         <f>$N$40</f>
         <v>0.14349999999999999</v>
       </c>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="33" t="s">
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="H36" s="37">
+      <c r="H36" s="31">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I36" s="37">
+      <c r="I36" s="31">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="32"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="26"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="26"/>
     </row>
     <row r="37" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="13" t="s">
@@ -6249,45 +6257,45 @@
       </c>
       <c r="B37" s="1">
         <f>C32*C37</f>
-        <v>7763641.909134998</v>
-      </c>
-      <c r="C37" s="37">
+        <v>924478.97354749986</v>
+      </c>
+      <c r="C37" s="31">
         <f>$N$40</f>
         <v>0.14349999999999999</v>
       </c>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="32"/>
-      <c r="J37" s="32"/>
-      <c r="K37" s="32"/>
-      <c r="M37" s="29" t="s">
-        <v>273</v>
-      </c>
-      <c r="N37" s="30"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+      <c r="K37" s="26"/>
+      <c r="M37" s="91" t="s">
+        <v>272</v>
+      </c>
+      <c r="N37" s="92"/>
     </row>
     <row r="38" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="B38" s="26">
+      <c r="B38" s="24">
         <f>C33*C38</f>
-        <v>7763818.8259799993</v>
-      </c>
-      <c r="C38" s="37">
+        <v>924036.68143499992</v>
+      </c>
+      <c r="C38" s="31">
         <f>$N$40</f>
         <v>0.14349999999999999</v>
       </c>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="32"/>
-      <c r="J38" s="32"/>
-      <c r="K38" s="32"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="26"/>
+      <c r="K38" s="26"/>
       <c r="M38" s="13" t="s">
         <v>183</v>
       </c>
@@ -6299,19 +6307,19 @@
       <c r="A39" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="B39" s="71">
+      <c r="B39" s="104">
         <f>SUM(B36:B38)</f>
-        <v>144913826.15741497</v>
-      </c>
-      <c r="C39" s="72"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="32"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="32"/>
+        <v>17251603.848062497</v>
+      </c>
+      <c r="C39" s="105"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
+      <c r="K39" s="26"/>
       <c r="M39" s="13" t="s">
         <v>185</v>
       </c>
@@ -6323,57 +6331,57 @@
       <c r="A40" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="B40" s="71">
+      <c r="B40" s="104">
         <f>B39*365.25</f>
-        <v>52929775003.995819</v>
-      </c>
-      <c r="C40" s="72"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="32"/>
-      <c r="J40" s="32"/>
-      <c r="K40" s="32"/>
+        <v>6301148305.5048265</v>
+      </c>
+      <c r="C40" s="105"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="26"/>
+      <c r="K40" s="26"/>
       <c r="M40" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="N40" s="37">
+      <c r="N40" s="31">
         <v>0.14349999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="43"/>
-      <c r="B41" s="44"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="32"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="32"/>
+      <c r="A41" s="37"/>
+      <c r="B41" s="38"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
     </row>
     <row r="42" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="89" t="s">
         <v>198</v>
       </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="29" t="s">
+      <c r="B42" s="90"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="91" t="s">
         <v>199</v>
       </c>
-      <c r="E42" s="30"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="73" t="s">
+      <c r="E42" s="92"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="93" t="s">
         <v>200</v>
       </c>
-      <c r="H42" s="74"/>
-      <c r="I42" s="75"/>
-      <c r="J42" s="46"/>
-      <c r="K42" s="46"/>
+      <c r="H42" s="94"/>
+      <c r="I42" s="95"/>
+      <c r="J42" s="40"/>
+      <c r="K42" s="40"/>
     </row>
     <row r="43" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="11" t="s">
@@ -6382,15 +6390,15 @@
       <c r="B43" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="C43" s="32"/>
-      <c r="D43" s="19">
+      <c r="C43" s="26"/>
+      <c r="D43" s="17">
         <f>(E10)-B3-(B4/60)</f>
         <v>14.833333333333334</v>
       </c>
-      <c r="E43" s="45" t="s">
+      <c r="E43" s="39" t="s">
         <v>203</v>
       </c>
-      <c r="F43" s="32"/>
+      <c r="F43" s="26"/>
       <c r="G43" s="12" t="s">
         <v>122</v>
       </c>
@@ -6411,29 +6419,28 @@
       <c r="A44" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="B44" s="47">
-        <f>$D$43*3600/B24</f>
-        <v>0.14651934247387208</v>
-      </c>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="32"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="48" t="s">
+      <c r="B44" s="108">
+        <v>0.18</v>
+      </c>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="42" t="s">
         <v>208</v>
       </c>
-      <c r="H44" s="49">
+      <c r="H44" s="43">
         <f>B3</f>
         <v>1</v>
       </c>
-      <c r="I44" s="50">
+      <c r="I44" s="44">
         <v>1</v>
       </c>
-      <c r="J44" s="51">
+      <c r="J44" s="45">
         <f>I44-H44</f>
         <v>0</v>
       </c>
-      <c r="K44" s="48" t="s">
+      <c r="K44" s="42" t="s">
         <v>203</v>
       </c>
     </row>
@@ -6441,32 +6448,31 @@
       <c r="A45" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="B45" s="47">
-        <f>$D$43*3600/B25</f>
-        <v>2.1366837387964148</v>
-      </c>
-      <c r="C45" s="32"/>
-      <c r="D45" s="29" t="s">
+      <c r="B45" s="108">
+        <v>0.18</v>
+      </c>
+      <c r="C45" s="26"/>
+      <c r="D45" s="91" t="s">
         <v>210</v>
       </c>
-      <c r="E45" s="30"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="48" t="s">
+      <c r="E45" s="92"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="H45" s="49">
+      <c r="H45" s="43">
         <f>B4/60</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="I45" s="110">
+      <c r="I45" s="84">
         <f>10/60</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="J45" s="51">
-        <f t="shared" ref="J45:J61" si="0">I45-H45</f>
+      <c r="J45" s="45">
+        <f t="shared" ref="J45:J61" si="1">I45-H45</f>
         <v>0</v>
       </c>
-      <c r="K45" s="48" t="s">
+      <c r="K45" s="42" t="s">
         <v>203</v>
       </c>
     </row>
@@ -6474,91 +6480,90 @@
       <c r="A46" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="B46" s="47">
-        <f>$D$43*3600/B26</f>
-        <v>1.8314013306811168</v>
-      </c>
-      <c r="C46" s="32"/>
-      <c r="D46" s="19">
+      <c r="B46" s="108">
+        <v>0.18</v>
+      </c>
+      <c r="C46" s="26"/>
+      <c r="D46" s="17">
         <f>3600/B5</f>
-        <v>0.18</v>
-      </c>
-      <c r="E46" s="33" t="s">
+        <v>2.1364985163204748</v>
+      </c>
+      <c r="E46" s="27" t="s">
         <v>213</v>
       </c>
-      <c r="F46" s="32"/>
-      <c r="G46" s="48" t="s">
+      <c r="F46" s="26"/>
+      <c r="G46" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="H46" s="49">
+      <c r="H46" s="43">
         <f>B5</f>
-        <v>20000</v>
-      </c>
-      <c r="I46" s="50">
-        <v>21000</v>
-      </c>
-      <c r="J46" s="51">
-        <f t="shared" si="0"/>
-        <v>1000</v>
-      </c>
-      <c r="K46" s="48" t="s">
+        <v>1685</v>
+      </c>
+      <c r="I46" s="44">
+        <v>1800</v>
+      </c>
+      <c r="J46" s="45">
+        <f t="shared" si="1"/>
+        <v>115</v>
+      </c>
+      <c r="K46" s="42" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="34"/>
-      <c r="B47" s="32"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="19">
+      <c r="A47" s="28"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="17">
         <f>D46/3600</f>
-        <v>4.9999999999999996E-5</v>
-      </c>
-      <c r="E47" s="33" t="s">
+        <v>5.9347181008902075E-4</v>
+      </c>
+      <c r="E47" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="F47" s="32"/>
-      <c r="G47" s="48" t="s">
+      <c r="F47" s="26"/>
+      <c r="G47" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="H47" s="49">
+      <c r="H47" s="43">
         <f>B6</f>
         <v>2</v>
       </c>
-      <c r="I47" s="50">
+      <c r="I47" s="44">
         <v>2</v>
       </c>
-      <c r="J47" s="51">
-        <f t="shared" si="0"/>
+      <c r="J47" s="45">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K47" s="48" t="s">
+      <c r="K47" s="42" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="63" t="s">
+      <c r="A48" s="96" t="s">
         <v>216</v>
       </c>
-      <c r="B48" s="64"/>
-      <c r="C48" s="32"/>
-      <c r="D48" s="32"/>
-      <c r="E48" s="32"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="48" t="s">
+      <c r="B48" s="97"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="H48" s="49">
+      <c r="H48" s="43">
         <f>B7</f>
         <v>8</v>
       </c>
-      <c r="I48" s="50">
+      <c r="I48" s="44">
         <v>8</v>
       </c>
-      <c r="J48" s="51">
-        <f t="shared" si="0"/>
+      <c r="J48" s="45">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K48" s="48" t="s">
+      <c r="K48" s="42" t="s">
         <v>203</v>
       </c>
     </row>
@@ -6569,27 +6574,27 @@
       <c r="B49" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="32"/>
-      <c r="D49" s="29" t="s">
+      <c r="C49" s="26"/>
+      <c r="D49" s="91" t="s">
         <v>218</v>
       </c>
-      <c r="E49" s="30"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="48" t="s">
+      <c r="E49" s="92"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="42" t="s">
         <v>210</v>
       </c>
-      <c r="H49" s="49">
+      <c r="H49" s="43">
         <f>D47</f>
-        <v>4.9999999999999996E-5</v>
-      </c>
-      <c r="I49" s="50">
+        <v>5.9347181008902075E-4</v>
+      </c>
+      <c r="I49" s="44">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="J49" s="51">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K49" s="48" t="s">
+      <c r="J49" s="45">
+        <f t="shared" si="1"/>
+        <v>-5.4347181008902073E-4</v>
+      </c>
+      <c r="K49" s="42" t="s">
         <v>219</v>
       </c>
     </row>
@@ -6597,36 +6602,34 @@
       <c r="A50" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="B50" s="19">
+      <c r="B50" s="17">
         <v>1.5</v>
       </c>
-      <c r="C50" s="32"/>
-      <c r="D50" s="47">
-        <v>210000</v>
-      </c>
-      <c r="E50" s="33" t="s">
+      <c r="C50" s="26"/>
+      <c r="D50" s="108">
+        <f>25000</f>
+        <v>25000</v>
+      </c>
+      <c r="E50" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="F50" s="19">
-        <f>B5*(D43-D60)</f>
-        <v>223333.33333333334</v>
-      </c>
-      <c r="G50" s="48" t="s">
+      <c r="F50" s="17"/>
+      <c r="G50" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="H50" s="49">
+      <c r="H50" s="43">
         <f>D50</f>
-        <v>210000</v>
-      </c>
-      <c r="I50" s="50">
+        <v>25000</v>
+      </c>
+      <c r="I50" s="44">
         <f>H50+H50*0.02</f>
-        <v>214200</v>
-      </c>
-      <c r="J50" s="51">
-        <f t="shared" si="0"/>
-        <v>4200</v>
-      </c>
-      <c r="K50" s="48" t="s">
+        <v>25500</v>
+      </c>
+      <c r="J50" s="45">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="K50" s="42" t="s">
         <v>184</v>
       </c>
     </row>
@@ -6634,29 +6637,29 @@
       <c r="A51" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="B51" s="19">
+      <c r="B51" s="17">
         <v>2</v>
       </c>
-      <c r="C51" s="32"/>
-      <c r="D51" s="32"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="48" t="s">
+      <c r="C51" s="26"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="42" t="s">
         <v>223</v>
       </c>
-      <c r="H51" s="49">
+      <c r="H51" s="43">
         <f>D60</f>
         <v>3.6666666666666665</v>
       </c>
-      <c r="I51" s="50">
+      <c r="I51" s="44">
         <f>H51-H51*0.01</f>
         <v>3.63</v>
       </c>
-      <c r="J51" s="51">
-        <f t="shared" si="0"/>
+      <c r="J51" s="45">
+        <f t="shared" si="1"/>
         <v>-3.6666666666666625E-2</v>
       </c>
-      <c r="K51" s="48" t="s">
+      <c r="K51" s="42" t="s">
         <v>203</v>
       </c>
     </row>
@@ -6664,31 +6667,31 @@
       <c r="A52" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="B52" s="19">
+      <c r="B52" s="17">
         <v>0.18</v>
       </c>
-      <c r="C52" s="32"/>
-      <c r="D52" s="27" t="s">
+      <c r="C52" s="26"/>
+      <c r="D52" s="85" t="s">
         <v>225</v>
       </c>
-      <c r="E52" s="28"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="52" t="s">
+      <c r="E52" s="86"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="46" t="s">
         <v>226</v>
       </c>
-      <c r="H52" s="49">
+      <c r="H52" s="43">
         <f>D43</f>
         <v>14.833333333333334</v>
       </c>
-      <c r="I52" s="50">
+      <c r="I52" s="44">
         <f>(I47*I48)-I44-I45</f>
         <v>14.833333333333334</v>
       </c>
-      <c r="J52" s="51">
-        <f t="shared" si="0"/>
+      <c r="J52" s="45">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K52" s="48" t="s">
+      <c r="K52" s="42" t="s">
         <v>203</v>
       </c>
     </row>
@@ -6696,34 +6699,34 @@
       <c r="A53" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="B53" s="19">
+      <c r="B53" s="17">
         <v>1</v>
       </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="53">
+      <c r="C53" s="26"/>
+      <c r="D53" s="47">
         <f>D50/B27</f>
-        <v>0.5016638517750539</v>
-      </c>
-      <c r="E53" s="45" t="s">
+        <v>5.972188711607785E-2</v>
+      </c>
+      <c r="E53" s="39" t="s">
         <v>228</v>
       </c>
-      <c r="F53" s="32"/>
-      <c r="G53" s="23" t="s">
+      <c r="F53" s="26"/>
+      <c r="G53" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="H53" s="107">
+      <c r="H53" s="81">
         <f>B31</f>
-        <v>182835</v>
-      </c>
-      <c r="I53" s="50">
+        <v>21766</v>
+      </c>
+      <c r="I53" s="44">
         <f>ROUND($I$50*C24,0)</f>
-        <v>186483</v>
-      </c>
-      <c r="J53" s="51">
-        <f t="shared" si="0"/>
-        <v>3648</v>
-      </c>
-      <c r="K53" s="48" t="s">
+        <v>22200</v>
+      </c>
+      <c r="J53" s="45">
+        <f t="shared" si="1"/>
+        <v>434</v>
+      </c>
+      <c r="K53" s="42" t="s">
         <v>184</v>
       </c>
     </row>
@@ -6731,29 +6734,29 @@
       <c r="A54" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="B54" s="19">
+      <c r="B54" s="17">
         <v>2</v>
       </c>
-      <c r="C54" s="32"/>
-      <c r="D54" s="44"/>
-      <c r="E54" s="44"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="23" t="s">
+      <c r="C54" s="26"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="H54" s="107">
+      <c r="H54" s="81">
         <f>B32</f>
-        <v>12538</v>
-      </c>
-      <c r="I54" s="50">
+        <v>1493</v>
+      </c>
+      <c r="I54" s="44">
         <f>ROUND($I$50*C25,0)</f>
-        <v>12788</v>
-      </c>
-      <c r="J54" s="51">
-        <f t="shared" si="0"/>
-        <v>250</v>
-      </c>
-      <c r="K54" s="48" t="s">
+        <v>1522</v>
+      </c>
+      <c r="J54" s="45">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="K54" s="42" t="s">
         <v>184</v>
       </c>
     </row>
@@ -6761,31 +6764,31 @@
       <c r="A55" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="B55" s="19">
+      <c r="B55" s="17">
         <v>0.5</v>
       </c>
-      <c r="C55" s="32"/>
-      <c r="D55" s="76" t="s">
+      <c r="C55" s="26"/>
+      <c r="D55" s="87" t="s">
         <v>231</v>
       </c>
-      <c r="E55" s="77"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="23" t="s">
+      <c r="E55" s="88"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="H55" s="107">
+      <c r="H55" s="81">
         <f>B33</f>
-        <v>14628</v>
-      </c>
-      <c r="I55" s="50">
+        <v>1741</v>
+      </c>
+      <c r="I55" s="44">
         <f>ROUND($I$50*C26,0)</f>
-        <v>14930</v>
-      </c>
-      <c r="J55" s="51">
-        <f t="shared" si="0"/>
-        <v>302</v>
-      </c>
-      <c r="K55" s="48" t="s">
+        <v>1777</v>
+      </c>
+      <c r="J55" s="45">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="K55" s="42" t="s">
         <v>184</v>
       </c>
     </row>
@@ -6793,34 +6796,34 @@
       <c r="A56" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="B56" s="19">
+      <c r="B56" s="17">
         <v>10</v>
       </c>
-      <c r="C56" s="32"/>
-      <c r="D56" s="19">
+      <c r="C56" s="26"/>
+      <c r="D56" s="17">
         <f>B3+(B4/60)</f>
         <v>1.1666666666666667</v>
       </c>
-      <c r="E56" s="33" t="s">
+      <c r="E56" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="F56" s="32"/>
-      <c r="G56" s="23" t="s">
+      <c r="F56" s="26"/>
+      <c r="G56" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="H56" s="54">
+      <c r="H56" s="48">
         <f>B36</f>
-        <v>129386365.42229998</v>
-      </c>
-      <c r="I56" s="55">
+        <v>15403088.193079997</v>
+      </c>
+      <c r="I56" s="49">
         <f>I53*E3*$N$35*$N$40</f>
-        <v>131967936.02453998</v>
-      </c>
-      <c r="J56" s="108">
-        <f t="shared" si="0"/>
-        <v>2581570.6022399962</v>
-      </c>
-      <c r="K56" s="48" t="s">
+        <v>15710215.835999997</v>
+      </c>
+      <c r="J56" s="82">
+        <f t="shared" si="1"/>
+        <v>307127.64292000048</v>
+      </c>
+      <c r="K56" s="42" t="s">
         <v>233</v>
       </c>
     </row>
@@ -6828,29 +6831,29 @@
       <c r="A57" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="B57" s="19">
+      <c r="B57" s="17">
         <v>90</v>
       </c>
-      <c r="C57" s="32"/>
-      <c r="D57" s="32"/>
-      <c r="E57" s="32"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="23" t="s">
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="H57" s="54">
+      <c r="H57" s="48">
         <f>B37</f>
-        <v>7763641.909134998</v>
-      </c>
-      <c r="I57" s="55">
+        <v>924478.97354749986</v>
+      </c>
+      <c r="I57" s="49">
         <f>I54*E4*$N$35*$N$40</f>
-        <v>7918444.1485099988</v>
-      </c>
-      <c r="J57" s="108">
-        <f t="shared" si="0"/>
-        <v>154802.23937500082</v>
-      </c>
-      <c r="K57" s="33" t="s">
+        <v>942436.03331499978</v>
+      </c>
+      <c r="J57" s="82">
+        <f t="shared" si="1"/>
+        <v>17957.059767499915</v>
+      </c>
+      <c r="K57" s="27" t="s">
         <v>233</v>
       </c>
     </row>
@@ -6858,31 +6861,31 @@
       <c r="A58" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="B58" s="19">
+      <c r="B58" s="17">
         <v>180</v>
       </c>
-      <c r="C58" s="32"/>
-      <c r="D58" s="76" t="s">
+      <c r="C58" s="26"/>
+      <c r="D58" s="87" t="s">
         <v>236</v>
       </c>
-      <c r="E58" s="77"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="23" t="s">
+      <c r="E58" s="88"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="H58" s="54">
+      <c r="H58" s="48">
         <f>B38</f>
-        <v>7763818.8259799993</v>
-      </c>
-      <c r="I58" s="55">
+        <v>924036.68143499992</v>
+      </c>
+      <c r="I58" s="49">
         <f>I55*E5*$N$35*$N$40</f>
-        <v>7924105.4875499988</v>
-      </c>
-      <c r="J58" s="108">
-        <f t="shared" si="0"/>
-        <v>160286.66156999953</v>
-      </c>
-      <c r="K58" s="33" t="s">
+        <v>943143.70069499989</v>
+      </c>
+      <c r="J58" s="82">
+        <f t="shared" si="1"/>
+        <v>19107.019259999972</v>
+      </c>
+      <c r="K58" s="27" t="s">
         <v>233</v>
       </c>
     </row>
@@ -6890,34 +6893,34 @@
       <c r="A59" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="B59" s="99">
+      <c r="B59" s="74">
         <f>D56*3600</f>
         <v>4200</v>
       </c>
-      <c r="C59" s="32"/>
-      <c r="D59" s="47">
+      <c r="C59" s="26"/>
+      <c r="D59" s="41">
         <v>220</v>
       </c>
-      <c r="E59" s="33" t="s">
+      <c r="E59" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="F59" s="32"/>
+      <c r="F59" s="26"/>
       <c r="G59" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="H59" s="54">
+      <c r="H59" s="48">
         <f>B40</f>
-        <v>52929775003.995819</v>
+        <v>6301148305.5048265</v>
       </c>
       <c r="I59" s="15">
         <f>SUM(I56:I58)*365.25</f>
-        <v>53987779887.534142</v>
-      </c>
-      <c r="J59" s="108">
-        <f t="shared" si="0"/>
-        <v>1058004883.5383224</v>
-      </c>
-      <c r="K59" s="33" t="s">
+        <v>6426864331.9461508</v>
+      </c>
+      <c r="J59" s="109">
+        <f>I59-H59</f>
+        <v>125716026.44132423</v>
+      </c>
+      <c r="K59" s="27" t="s">
         <v>233</v>
       </c>
     </row>
@@ -6925,202 +6928,223 @@
       <c r="A60" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="B60" s="103">
+      <c r="B60" s="78">
         <f>SUM(B50:B59)</f>
         <v>4487.18</v>
       </c>
-      <c r="C60" s="32"/>
-      <c r="D60" s="47">
+      <c r="C60" s="26"/>
+      <c r="D60" s="41">
         <f>D59/60</f>
         <v>3.6666666666666665</v>
       </c>
-      <c r="E60" s="33" t="s">
+      <c r="E60" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="F60" s="32"/>
+      <c r="F60" s="26"/>
       <c r="G60" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="H60" s="50">
+        <f>B66</f>
+        <v>0.93984962406015038</v>
+      </c>
+      <c r="I60" s="31">
+        <f>I50/26600</f>
+        <v>0.95864661654135341</v>
+      </c>
+      <c r="J60" s="45">
+        <f t="shared" si="1"/>
+        <v>1.8796992481203034E-2</v>
+      </c>
+      <c r="K60" s="27" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="28"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="H60" s="56">
-        <f>B66</f>
-        <v>0.94029850746268628</v>
-      </c>
-      <c r="I60" s="37">
-        <f>I49*I50/(I52-I51)</f>
-        <v>0.95596548646236246</v>
-      </c>
-      <c r="J60" s="51">
-        <f t="shared" si="0"/>
-        <v>1.5666978999676173E-2</v>
-      </c>
-      <c r="K60" s="33" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="34"/>
-      <c r="B61" s="32"/>
-      <c r="C61" s="32"/>
-      <c r="D61" s="32"/>
-      <c r="E61" s="32"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="H61" s="56">
+      <c r="H61" s="50">
         <f>B64</f>
         <v>0.75280898876404501</v>
       </c>
-      <c r="I61" s="57">
+      <c r="I61" s="51">
         <f>(I52-I51)/I52</f>
         <v>0.75528089887640448</v>
       </c>
-      <c r="J61" s="51">
-        <f t="shared" si="0"/>
+      <c r="J61" s="45">
+        <f t="shared" si="1"/>
         <v>2.4719101123594767E-3</v>
       </c>
-      <c r="K61" s="48" t="s">
+      <c r="K61" s="42" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="16" t="s">
+      <c r="A62" s="89" t="s">
+        <v>240</v>
+      </c>
+      <c r="B62" s="90"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="91" t="s">
         <v>241</v>
       </c>
-      <c r="B62" s="17"/>
-      <c r="C62" s="32"/>
-      <c r="D62" s="29" t="s">
+      <c r="E62" s="92"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="H62" s="50">
+        <f>B65</f>
+        <v>0.99609999999999999</v>
+      </c>
+      <c r="I62" s="51">
+        <f>99.61%</f>
+        <v>0.99609999999999999</v>
+      </c>
+      <c r="J62" s="45">
+        <f t="shared" ref="J62" si="2">I62-H62</f>
+        <v>0</v>
+      </c>
+      <c r="K62" s="42" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="B63" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="E62" s="30"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="42"/>
-      <c r="H62" s="38"/>
-      <c r="I62" s="42"/>
-      <c r="J62" s="38"/>
-      <c r="K62" s="42"/>
-    </row>
-    <row r="63" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="58" t="s">
-        <v>122</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="C63" s="32"/>
-      <c r="D63" s="33" t="s">
+      <c r="C63" s="26"/>
+      <c r="D63" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="E63" s="37">
+      <c r="E63" s="31">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="F63" s="32"/>
-      <c r="G63" s="42"/>
-      <c r="H63" s="38"/>
-      <c r="I63" s="42"/>
-      <c r="J63" s="38"/>
-      <c r="K63" s="42"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="H63" s="50">
+        <f>B67</f>
+        <v>0.70476788882318153</v>
+      </c>
+      <c r="I63" s="51">
+        <f>I60*I61*I62</f>
+        <v>0.72122369308101708</v>
+      </c>
+      <c r="J63" s="45">
+        <f t="shared" ref="J63" si="3">I63-H63</f>
+        <v>1.6455804257835549E-2</v>
+      </c>
+      <c r="K63" s="42" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="64" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="B64" s="37">
+        <v>239</v>
+      </c>
+      <c r="B64" s="31">
         <f>(D43-D60)/D43</f>
         <v>0.75280898876404501</v>
       </c>
-      <c r="C64" s="32"/>
-      <c r="D64" s="33" t="s">
-        <v>244</v>
-      </c>
-      <c r="E64" s="35">
+      <c r="C64" s="26"/>
+      <c r="D64" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="E64" s="29">
         <v>0.02</v>
       </c>
-      <c r="F64" s="32"/>
-      <c r="G64" s="42"/>
-      <c r="H64" s="38"/>
-      <c r="I64" s="42"/>
-      <c r="J64" s="38"/>
-      <c r="K64" s="42"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="36"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="36"/>
+      <c r="J64" s="32"/>
+      <c r="K64" s="36"/>
     </row>
     <row r="65" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="B65" s="37">
+        <v>244</v>
+      </c>
+      <c r="B65" s="31">
         <f>E65</f>
         <v>0.99609999999999999</v>
       </c>
-      <c r="C65" s="32"/>
-      <c r="D65" s="33" t="s">
-        <v>246</v>
-      </c>
-      <c r="E65" s="37">
+      <c r="C65" s="26"/>
+      <c r="D65" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="E65" s="31">
         <f>1-E63</f>
         <v>0.99609999999999999</v>
       </c>
-      <c r="F65" s="32"/>
-      <c r="G65" s="32"/>
-      <c r="H65" s="32"/>
-      <c r="I65" s="32"/>
-      <c r="J65" s="38"/>
-      <c r="K65" s="32"/>
+      <c r="F65" s="26"/>
+      <c r="G65" s="26"/>
+      <c r="H65" s="26"/>
+      <c r="I65" s="26"/>
+      <c r="J65" s="32"/>
+      <c r="K65" s="26"/>
     </row>
     <row r="66" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="59" t="s">
-        <v>239</v>
-      </c>
-      <c r="B66" s="60">
-        <f>D50*D47/(D43-D60)</f>
-        <v>0.94029850746268628</v>
-      </c>
-      <c r="C66" s="61"/>
-      <c r="D66" s="33" t="s">
-        <v>247</v>
-      </c>
-      <c r="E66" s="35">
+      <c r="A66" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="B66" s="110">
+        <f>D50/26600</f>
+        <v>0.93984962406015038</v>
+      </c>
+      <c r="C66" s="111"/>
+      <c r="D66" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="E66" s="29">
         <f>1-E64</f>
         <v>0.98</v>
       </c>
-      <c r="F66" s="32"/>
-      <c r="G66" s="32"/>
-      <c r="H66" s="32"/>
-      <c r="I66" s="32"/>
-      <c r="J66" s="38"/>
-      <c r="K66" s="32"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="26"/>
+      <c r="H66" s="26"/>
+      <c r="I66" s="26"/>
+      <c r="J66" s="32"/>
+      <c r="K66" s="26"/>
     </row>
     <row r="67" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="B67" s="62">
+        <v>247</v>
+      </c>
+      <c r="B67" s="53">
         <f>B66*B65*B64</f>
-        <v>0.70510449438202227</v>
-      </c>
-      <c r="C67" s="32"/>
-      <c r="D67" s="44"/>
-      <c r="E67" s="44"/>
-      <c r="F67" s="32"/>
-      <c r="G67" s="32"/>
-      <c r="H67" s="32"/>
-      <c r="I67" s="32"/>
-      <c r="J67" s="32"/>
-      <c r="K67" s="32"/>
+        <v>0.70476788882318153</v>
+      </c>
+      <c r="C67" s="26"/>
+      <c r="D67" s="38"/>
+      <c r="E67" s="38"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="26"/>
+      <c r="H67" s="26"/>
+      <c r="I67" s="26"/>
+      <c r="J67" s="26"/>
+      <c r="K67" s="26"/>
     </row>
     <row r="68" spans="1:11" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="D45:E45"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="D49:E49"/>
@@ -7130,12 +7154,17 @@
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B40:C40"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:E62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7148,641 +7177,641 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.6640625" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" style="86" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" style="63" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="15.33203125" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" customWidth="1"/>
     <col min="6" max="6" width="19.109375" customWidth="1"/>
-    <col min="7" max="7" width="18.109375" style="95" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" style="70" customWidth="1"/>
     <col min="8" max="8" width="18.109375" customWidth="1"/>
     <col min="9" max="9" width="18.21875" customWidth="1"/>
     <col min="10" max="10" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="56" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1" s="57" t="s">
         <v>257</v>
       </c>
-      <c r="B1" s="80" t="s">
+      <c r="C1" s="57" t="s">
         <v>258</v>
       </c>
-      <c r="C1" s="80" t="s">
+      <c r="D1" s="57" t="s">
         <v>259</v>
       </c>
-      <c r="D1" s="80" t="s">
+      <c r="E1" s="57" t="s">
         <v>260</v>
       </c>
-      <c r="E1" s="80" t="s">
+      <c r="F1" s="57" t="s">
         <v>261</v>
       </c>
-      <c r="F1" s="80" t="s">
+      <c r="G1" s="68" t="s">
         <v>262</v>
       </c>
-      <c r="G1" s="93" t="s">
+      <c r="I1" s="106" t="s">
         <v>263</v>
       </c>
-      <c r="I1" s="91" t="s">
-        <v>264</v>
-      </c>
-      <c r="J1" s="92"/>
+      <c r="J1" s="107"/>
     </row>
     <row r="2" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="81">
+      <c r="A2" s="58">
         <v>1</v>
       </c>
-      <c r="B2" s="83">
+      <c r="B2" s="60">
         <f>'EX+Beneficios'!B11+'EX+Beneficios'!B21</f>
         <v>-912716600</v>
       </c>
-      <c r="C2" s="82">
+      <c r="C2" s="59">
         <v>0</v>
       </c>
-      <c r="D2" s="87">
+      <c r="D2" s="64">
         <f>C2+B2</f>
         <v>-912716600</v>
       </c>
-      <c r="E2" s="87">
+      <c r="E2" s="64">
         <f>D2</f>
         <v>-912716600</v>
       </c>
-      <c r="F2" s="84">
+      <c r="F2" s="61">
         <f>NPV($J$2,D2)</f>
         <v>-827860861.6780045</v>
       </c>
-      <c r="G2" s="94">
+      <c r="G2" s="69">
         <f>F2/-$D$2</f>
         <v>-0.90702947845804982</v>
       </c>
-      <c r="I2" s="88" t="s">
+      <c r="I2" s="65" t="s">
+        <v>264</v>
+      </c>
+      <c r="J2" s="66">
+        <v>0.10249999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="58">
+        <v>2</v>
+      </c>
+      <c r="B3" s="60">
+        <f>'EX+Beneficios'!B11+'EX+Beneficios'!B28</f>
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C3" s="60">
+        <f>'EX+Beneficios'!B28</f>
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D3" s="64">
+        <f t="shared" ref="D3:D21" si="0">C3+B3</f>
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E3" s="64">
+        <f>E2+D3</f>
+        <v>-707318219.11735153</v>
+      </c>
+      <c r="F3" s="61">
+        <f>NPV($J$2,$D$2:D3)</f>
+        <v>-658879105.4076041</v>
+      </c>
+      <c r="G3" s="69">
+        <f t="shared" ref="G3:G21" si="1">F3/-$D$2</f>
+        <v>-0.72188793915614557</v>
+      </c>
+      <c r="I3" s="65" t="s">
         <v>265</v>
       </c>
-      <c r="J2" s="89">
-        <v>0.10249999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="81">
-        <v>2</v>
-      </c>
-      <c r="B3" s="83">
-        <f>B2</f>
-        <v>-912716600</v>
-      </c>
-      <c r="C3" s="83">
-        <f>'EX+Beneficios'!B28</f>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D3" s="87">
-        <f t="shared" ref="D3:D21" si="0">C3+B3</f>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E3" s="87">
-        <f>E2+D3</f>
-        <v>-704195152.46167755</v>
-      </c>
-      <c r="F3" s="84">
-        <f>NPV($J$2,$D$2:D3)</f>
-        <v>-656309750.74104106</v>
-      </c>
-      <c r="G3" s="94">
-        <f t="shared" ref="G3:G21" si="1">F3/-$D$2</f>
-        <v>-0.71907287622580884</v>
-      </c>
-      <c r="I3" s="88" t="s">
+      <c r="J3" s="71">
+        <f>A21+(-E21/D21)</f>
+        <v>5.4436406756364253</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="58">
+        <v>3</v>
+      </c>
+      <c r="B4" s="60">
+        <f>B3</f>
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C4" s="60">
+        <f>C3</f>
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D4" s="64">
+        <f t="shared" si="0"/>
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E4" s="64">
+        <f t="shared" ref="E4:E21" si="2">E3+D4</f>
+        <v>-501919838.23470306</v>
+      </c>
+      <c r="F4" s="61">
+        <f>NPV($J$2,$D$2:D4)</f>
+        <v>-505607671.14873743</v>
+      </c>
+      <c r="G4" s="69">
+        <f t="shared" si="1"/>
+        <v>-0.55395910532221881</v>
+      </c>
+      <c r="I4" s="67" t="s">
         <v>266</v>
       </c>
-      <c r="J3" s="96">
-        <f>A21+(-E21/D21)</f>
-        <v>5.3770873968840025</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="81">
-        <v>3</v>
-      </c>
-      <c r="B4" s="83">
-        <f t="shared" ref="B4:B21" si="2">B3</f>
-        <v>-912716600</v>
-      </c>
-      <c r="C4" s="83">
-        <f>C3</f>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D4" s="87">
+      <c r="J4" s="72">
+        <f>IRR(D2:D21)</f>
+        <v>0.2198861015497513</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="58">
+        <v>4</v>
+      </c>
+      <c r="B5" s="60">
+        <f t="shared" ref="B5:B21" si="3">B4</f>
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C5" s="60">
+        <f t="shared" ref="C5:C21" si="4">C4</f>
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D5" s="64">
         <f t="shared" si="0"/>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E4" s="87">
-        <f t="shared" ref="E4:E21" si="3">E3+D4</f>
-        <v>-495673704.9233551</v>
-      </c>
-      <c r="F4" s="84">
-        <f>NPV($J$2,$D$2:D4)</f>
-        <v>-500707836.05898803</v>
-      </c>
-      <c r="G4" s="94">
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E5" s="64">
+        <f t="shared" si="2"/>
+        <v>-296521457.3520546</v>
+      </c>
+      <c r="F5" s="61">
+        <f>NPV($J$2,$D$2:D5)</f>
+        <v>-366585962.0704003</v>
+      </c>
+      <c r="G5" s="69">
         <f t="shared" si="1"/>
-        <v>-0.54859069733035204</v>
-      </c>
-      <c r="I4" s="90" t="s">
-        <v>267</v>
-      </c>
-      <c r="J4" s="97">
-        <f>IRR(D2:D21)</f>
-        <v>0.22351674056187076</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="81">
-        <v>4</v>
-      </c>
-      <c r="B5" s="83">
+        <v>-0.40164270275176356</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="58">
+        <v>5</v>
+      </c>
+      <c r="B6" s="60">
+        <f t="shared" si="3"/>
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C6" s="60">
+        <f t="shared" si="4"/>
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D6" s="64">
+        <f t="shared" si="0"/>
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E6" s="64">
         <f t="shared" si="2"/>
-        <v>-912716600</v>
-      </c>
-      <c r="C5" s="83">
-        <f t="shared" ref="C5:C21" si="4">C4</f>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D5" s="87">
+        <v>-91123076.469406128</v>
+      </c>
+      <c r="F6" s="61">
+        <f>NPV($J$2,$D$2:D6)</f>
+        <v>-240489173.79072949</v>
+      </c>
+      <c r="G6" s="69">
+        <f t="shared" si="1"/>
+        <v>-0.26348723556767728</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="58">
+        <v>6</v>
+      </c>
+      <c r="B7" s="60">
+        <f t="shared" si="3"/>
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C7" s="60">
+        <f t="shared" si="4"/>
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D7" s="64">
         <f t="shared" si="0"/>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E5" s="87">
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E7" s="64">
+        <f t="shared" si="2"/>
+        <v>114275304.41324234</v>
+      </c>
+      <c r="F7" s="61">
+        <f>NPV($J$2,$D$2:D7)</f>
+        <v>-126115669.68218453</v>
+      </c>
+      <c r="G7" s="69">
+        <f t="shared" si="1"/>
+        <v>-0.13817615422156729</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="58">
+        <v>7</v>
+      </c>
+      <c r="B8" s="60">
         <f t="shared" si="3"/>
-        <v>-287152257.38503265</v>
-      </c>
-      <c r="F5" s="84">
-        <f>NPV($J$2,$D$2:D5)</f>
-        <v>-359572312.53785151</v>
-      </c>
-      <c r="G5" s="94">
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C8" s="60">
+        <f t="shared" si="4"/>
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D8" s="64">
+        <f t="shared" si="0"/>
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E8" s="64">
+        <f t="shared" si="2"/>
+        <v>319673685.29589081</v>
+      </c>
+      <c r="F8" s="61">
+        <f>NPV($J$2,$D$2:D8)</f>
+        <v>-22375529.901191369</v>
+      </c>
+      <c r="G8" s="69">
         <f t="shared" si="1"/>
-        <v>-0.39395833552041404</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="81">
-        <v>5</v>
-      </c>
-      <c r="B6" s="83">
+        <v>-2.4515309463190839E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="58">
+        <v>8</v>
+      </c>
+      <c r="B9" s="60">
+        <f t="shared" si="3"/>
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C9" s="60">
+        <f t="shared" si="4"/>
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D9" s="64">
+        <f t="shared" si="0"/>
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E9" s="64">
         <f t="shared" si="2"/>
-        <v>-912716600</v>
-      </c>
-      <c r="C6" s="83">
+        <v>525072066.17853928</v>
+      </c>
+      <c r="F9" s="61">
+        <f>NPV($J$2,$D$2:D9)</f>
+        <v>71719834.97952804</v>
+      </c>
+      <c r="G9" s="69">
+        <f t="shared" si="1"/>
+        <v>7.8578427279100693E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="58">
+        <v>9</v>
+      </c>
+      <c r="B10" s="60">
+        <f t="shared" si="3"/>
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C10" s="60">
         <f t="shared" si="4"/>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D6" s="87">
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D10" s="64">
         <f t="shared" si="0"/>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E6" s="87">
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E10" s="64">
+        <f t="shared" si="2"/>
+        <v>730470447.06118774</v>
+      </c>
+      <c r="F10" s="61">
+        <f>NPV($J$2,$D$2:D10)</f>
+        <v>157067104.71260688</v>
+      </c>
+      <c r="G10" s="69">
+        <f t="shared" si="1"/>
+        <v>0.17208748554875289</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="58">
+        <v>10</v>
+      </c>
+      <c r="B11" s="60">
         <f t="shared" si="3"/>
-        <v>-78630809.846710205</v>
-      </c>
-      <c r="F6" s="84">
-        <f>NPV($J$2,$D$2:D6)</f>
-        <v>-231558232.24657121</v>
-      </c>
-      <c r="G6" s="94">
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C11" s="60">
+        <f t="shared" si="4"/>
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D11" s="64">
+        <f t="shared" si="0"/>
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E11" s="64">
+        <f t="shared" si="2"/>
+        <v>935868827.94383621</v>
+      </c>
+      <c r="F11" s="61">
+        <f>NPV($J$2,$D$2:D11)</f>
+        <v>234479594.26641989</v>
+      </c>
+      <c r="G11" s="69">
         <f t="shared" si="1"/>
-        <v>-0.25370222503520939</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="81">
-        <v>6</v>
-      </c>
-      <c r="B7" s="83">
+        <v>0.25690295790217893</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="58">
+        <v>11</v>
+      </c>
+      <c r="B12" s="60">
+        <f t="shared" si="3"/>
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C12" s="60">
+        <f t="shared" si="4"/>
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D12" s="64">
+        <f t="shared" si="0"/>
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E12" s="64">
         <f t="shared" si="2"/>
-        <v>-912716600</v>
-      </c>
-      <c r="C7" s="83">
+        <v>1141267208.8264847</v>
+      </c>
+      <c r="F12" s="61">
+        <f>NPV($J$2,$D$2:D12)</f>
+        <v>304695004.29255408</v>
+      </c>
+      <c r="G12" s="69">
+        <f t="shared" si="1"/>
+        <v>0.33383309155608004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="58">
+        <v>12</v>
+      </c>
+      <c r="B13" s="60">
+        <f t="shared" si="3"/>
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C13" s="60">
         <f t="shared" si="4"/>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D7" s="87">
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D13" s="64">
         <f t="shared" si="0"/>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E7" s="87">
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E13" s="64">
+        <f t="shared" si="2"/>
+        <v>1346665589.7091331</v>
+      </c>
+      <c r="F13" s="61">
+        <f>NPV($J$2,$D$2:D13)</f>
+        <v>368382451.02827674</v>
+      </c>
+      <c r="G13" s="69">
+        <f t="shared" si="1"/>
+        <v>0.40361099056188604</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="58">
+        <v>13</v>
+      </c>
+      <c r="B14" s="60">
         <f t="shared" si="3"/>
-        <v>129890637.69161224</v>
-      </c>
-      <c r="F7" s="84">
-        <f>NPV($J$2,$D$2:D7)</f>
-        <v>-115445687.76468435</v>
-      </c>
-      <c r="G7" s="94">
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C14" s="60">
+        <f t="shared" si="4"/>
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D14" s="64">
+        <f t="shared" si="0"/>
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E14" s="64">
+        <f t="shared" si="2"/>
+        <v>1552063970.5917816</v>
+      </c>
+      <c r="F14" s="61">
+        <f>NPV($J$2,$D$2:D14)</f>
+        <v>426148842.6253041</v>
+      </c>
+      <c r="G14" s="69">
         <f t="shared" si="1"/>
-        <v>-0.12648579829125969</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="81">
-        <v>7</v>
-      </c>
-      <c r="B8" s="83">
+        <v>0.46690160190502078</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="58">
+        <v>14</v>
+      </c>
+      <c r="B15" s="60">
+        <f t="shared" si="3"/>
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C15" s="60">
+        <f t="shared" si="4"/>
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D15" s="64">
+        <f t="shared" si="0"/>
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E15" s="64">
         <f t="shared" si="2"/>
-        <v>-912716600</v>
-      </c>
-      <c r="C8" s="83">
+        <v>1757462351.4744301</v>
+      </c>
+      <c r="F15" s="61">
+        <f>NPV($J$2,$D$2:D15)</f>
+        <v>478544662.66795927</v>
+      </c>
+      <c r="G15" s="69">
+        <f t="shared" si="1"/>
+        <v>0.52430805210287534</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="58">
+        <v>15</v>
+      </c>
+      <c r="B16" s="60">
+        <f t="shared" si="3"/>
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C16" s="60">
         <f t="shared" si="4"/>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D8" s="87">
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D16" s="64">
         <f t="shared" si="0"/>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E8" s="87">
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E16" s="64">
+        <f t="shared" si="2"/>
+        <v>1962860732.3570786</v>
+      </c>
+      <c r="F16" s="61">
+        <f>NPV($J$2,$D$2:D16)</f>
+        <v>526069215.99463063</v>
+      </c>
+      <c r="G16" s="69">
+        <f t="shared" si="1"/>
+        <v>0.5763773946859635</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="58">
+        <v>16</v>
+      </c>
+      <c r="B17" s="60">
         <f t="shared" si="3"/>
-        <v>338412085.22993469</v>
-      </c>
-      <c r="F8" s="84">
-        <f>NPV($J$2,$D$2:D8)</f>
-        <v>-10128187.100841371</v>
-      </c>
-      <c r="G8" s="94">
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C17" s="60">
+        <f t="shared" si="4"/>
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D17" s="64">
+        <f t="shared" si="0"/>
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E17" s="64">
+        <f t="shared" si="2"/>
+        <v>2168259113.239727</v>
+      </c>
+      <c r="F17" s="61">
+        <f>NPV($J$2,$D$2:D17)</f>
+        <v>569175386.81247318</v>
+      </c>
+      <c r="G17" s="69">
         <f t="shared" si="1"/>
-        <v>-1.1096749090398237E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="81">
-        <v>8</v>
-      </c>
-      <c r="B9" s="83">
+        <v>0.62360582333275538</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="58">
+        <v>17</v>
+      </c>
+      <c r="B18" s="60">
+        <f t="shared" si="3"/>
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C18" s="60">
+        <f t="shared" si="4"/>
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D18" s="64">
+        <f t="shared" si="0"/>
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E18" s="64">
         <f t="shared" si="2"/>
-        <v>-912716600</v>
-      </c>
-      <c r="C9" s="83">
+        <v>2373657494.1223755</v>
+      </c>
+      <c r="F18" s="61">
+        <f>NPV($J$2,$D$2:D18)</f>
+        <v>608273954.44770443</v>
+      </c>
+      <c r="G18" s="69">
+        <f t="shared" si="1"/>
+        <v>0.66644340033664828</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="58">
+        <v>18</v>
+      </c>
+      <c r="B19" s="60">
+        <f t="shared" si="3"/>
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C19" s="60">
         <f t="shared" si="4"/>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D9" s="87">
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D19" s="64">
         <f t="shared" si="0"/>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E9" s="87">
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E19" s="64">
+        <f t="shared" si="2"/>
+        <v>2579055875.005024</v>
+      </c>
+      <c r="F19" s="61">
+        <f>NPV($J$2,$D$2:D19)</f>
+        <v>643737507.85834503</v>
+      </c>
+      <c r="G19" s="69">
+        <f t="shared" si="1"/>
+        <v>0.70529834546489567</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="58">
+        <v>19</v>
+      </c>
+      <c r="B20" s="60">
         <f t="shared" si="3"/>
-        <v>546933532.76825714</v>
-      </c>
-      <c r="F9" s="84">
-        <f>NPV($J$2,$D$2:D9)</f>
-        <v>85397890.598789439</v>
-      </c>
-      <c r="G9" s="94">
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C20" s="60">
+        <f t="shared" si="4"/>
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D20" s="64">
+        <f t="shared" si="0"/>
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E20" s="64">
+        <f t="shared" si="2"/>
+        <v>2784454255.8876724</v>
+      </c>
+      <c r="F20" s="61">
+        <f>NPV($J$2,$D$2:D20)</f>
+        <v>675903996.21266758</v>
+      </c>
+      <c r="G20" s="69">
         <f t="shared" si="1"/>
-        <v>9.3564520026029371E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="81">
-        <v>9</v>
-      </c>
-      <c r="B10" s="83">
+        <v>0.74054092608008615</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="58">
+        <v>20</v>
+      </c>
+      <c r="B21" s="60">
+        <f t="shared" si="3"/>
+        <v>16449190.441324234</v>
+      </c>
+      <c r="C21" s="60">
+        <f t="shared" si="4"/>
+        <v>188949190.44132423</v>
+      </c>
+      <c r="D21" s="64">
+        <f t="shared" si="0"/>
+        <v>205398380.88264847</v>
+      </c>
+      <c r="E21" s="64">
         <f t="shared" si="2"/>
-        <v>-912716600</v>
-      </c>
-      <c r="C10" s="83">
-        <f t="shared" si="4"/>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D10" s="87">
-        <f t="shared" si="0"/>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E10" s="87">
-        <f t="shared" si="3"/>
-        <v>755454980.30657959</v>
-      </c>
-      <c r="F10" s="84">
-        <f>NPV($J$2,$D$2:D10)</f>
-        <v>172042859.03382874</v>
-      </c>
-      <c r="G10" s="94">
+        <v>2989852636.7703209</v>
+      </c>
+      <c r="F21" s="61">
+        <f>NPV($J$2,$D$2:D21)</f>
+        <v>705079949.36851561</v>
+      </c>
+      <c r="G21" s="69">
         <f t="shared" si="1"/>
-        <v>0.18849537636746033</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="81">
-        <v>10</v>
-      </c>
-      <c r="B11" s="83">
-        <f t="shared" si="2"/>
-        <v>-912716600</v>
-      </c>
-      <c r="C11" s="83">
-        <f t="shared" si="4"/>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D11" s="87">
-        <f t="shared" si="0"/>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E11" s="87">
-        <f t="shared" si="3"/>
-        <v>963976427.84490204</v>
-      </c>
-      <c r="F11" s="84">
-        <f>NPV($J$2,$D$2:D11)</f>
-        <v>250632399.56447661</v>
-      </c>
-      <c r="G11" s="94">
-        <f t="shared" si="1"/>
-        <v>0.27460046148440448</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="81">
-        <v>11</v>
-      </c>
-      <c r="B12" s="83">
-        <f t="shared" si="2"/>
-        <v>-912716600</v>
-      </c>
-      <c r="C12" s="83">
-        <f t="shared" si="4"/>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D12" s="87">
-        <f t="shared" si="0"/>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E12" s="87">
-        <f t="shared" si="3"/>
-        <v>1172497875.3832245</v>
-      </c>
-      <c r="F12" s="84">
-        <f>NPV($J$2,$D$2:D12)</f>
-        <v>321915429.52424794</v>
-      </c>
-      <c r="G12" s="94">
-        <f t="shared" si="1"/>
-        <v>0.35270031193061235</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="81">
-        <v>12</v>
-      </c>
-      <c r="B13" s="83">
-        <f t="shared" si="2"/>
-        <v>-912716600</v>
-      </c>
-      <c r="C13" s="83">
-        <f t="shared" si="4"/>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D13" s="87">
-        <f t="shared" si="0"/>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E13" s="87">
-        <f t="shared" si="3"/>
-        <v>1381019322.9215469</v>
-      </c>
-      <c r="F13" s="84">
-        <f>NPV($J$2,$D$2:D13)</f>
-        <v>386571239.01156878</v>
-      </c>
-      <c r="G13" s="94">
-        <f t="shared" si="1"/>
-        <v>0.42353917854848788</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="81">
-        <v>13</v>
-      </c>
-      <c r="B14" s="83">
-        <f t="shared" si="2"/>
-        <v>-912716600</v>
-      </c>
-      <c r="C14" s="83">
-        <f t="shared" si="4"/>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D14" s="87">
-        <f t="shared" si="0"/>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E14" s="87">
-        <f t="shared" si="3"/>
-        <v>1589540770.4598694</v>
-      </c>
-      <c r="F14" s="84">
-        <f>NPV($J$2,$D$2:D14)</f>
-        <v>445215964.17013651</v>
-      </c>
-      <c r="G14" s="94">
-        <f t="shared" si="1"/>
-        <v>0.48779211879145895</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="81">
-        <v>14</v>
-      </c>
-      <c r="B15" s="83">
-        <f t="shared" si="2"/>
-        <v>-912716600</v>
-      </c>
-      <c r="C15" s="83">
-        <f t="shared" si="4"/>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D15" s="87">
-        <f t="shared" si="0"/>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E15" s="87">
-        <f t="shared" si="3"/>
-        <v>1798062217.9981918</v>
-      </c>
-      <c r="F15" s="84">
-        <f>NPV($J$2,$D$2:D15)</f>
-        <v>498408458.64502782</v>
-      </c>
-      <c r="G15" s="94">
-        <f t="shared" si="1"/>
-        <v>0.54607142966943711</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="81">
-        <v>15</v>
-      </c>
-      <c r="B16" s="83">
-        <f t="shared" si="2"/>
-        <v>-912716600</v>
-      </c>
-      <c r="C16" s="83">
-        <f t="shared" si="4"/>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D16" s="87">
-        <f t="shared" si="0"/>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E16" s="87">
-        <f t="shared" si="3"/>
-        <v>2006583665.5365143</v>
-      </c>
-      <c r="F16" s="84">
-        <f>NPV($J$2,$D$2:D16)</f>
-        <v>546655619.16647112</v>
-      </c>
-      <c r="G16" s="94">
-        <f t="shared" si="1"/>
-        <v>0.59893248261998422</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="81">
-        <v>16</v>
-      </c>
-      <c r="B17" s="83">
-        <f t="shared" si="2"/>
-        <v>-912716600</v>
-      </c>
-      <c r="C17" s="83">
-        <f t="shared" si="4"/>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D17" s="87">
-        <f t="shared" si="0"/>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E17" s="87">
-        <f t="shared" si="3"/>
-        <v>2215105113.0748367</v>
-      </c>
-      <c r="F17" s="84">
-        <f>NPV($J$2,$D$2:D17)</f>
-        <v>590417216.01131773</v>
-      </c>
-      <c r="G17" s="94">
-        <f t="shared" si="1"/>
-        <v>0.64687901590846242</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="81">
-        <v>17</v>
-      </c>
-      <c r="B18" s="83">
-        <f t="shared" si="2"/>
-        <v>-912716600</v>
-      </c>
-      <c r="C18" s="83">
-        <f t="shared" si="4"/>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D18" s="87">
-        <f t="shared" si="0"/>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E18" s="87">
-        <f t="shared" si="3"/>
-        <v>2423626560.6131592</v>
-      </c>
-      <c r="F18" s="84">
-        <f>NPV($J$2,$D$2:D18)</f>
-        <v>630110274.37399042</v>
-      </c>
-      <c r="G18" s="94">
-        <f t="shared" si="1"/>
-        <v>0.69036793499098237</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="81">
-        <v>18</v>
-      </c>
-      <c r="B19" s="83">
-        <f t="shared" si="2"/>
-        <v>-912716600</v>
-      </c>
-      <c r="C19" s="83">
-        <f t="shared" si="4"/>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D19" s="87">
-        <f t="shared" si="0"/>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E19" s="87">
-        <f t="shared" si="3"/>
-        <v>2632148008.1514816</v>
-      </c>
-      <c r="F19" s="84">
-        <f>NPV($J$2,$D$2:D19)</f>
-        <v>666113048.39909041</v>
-      </c>
-      <c r="G19" s="94">
-        <f t="shared" si="1"/>
-        <v>0.72981366658510471</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="81">
-        <v>19</v>
-      </c>
-      <c r="B20" s="83">
-        <f t="shared" si="2"/>
-        <v>-912716600</v>
-      </c>
-      <c r="C20" s="83">
-        <f t="shared" si="4"/>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D20" s="87">
-        <f t="shared" si="0"/>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E20" s="87">
-        <f t="shared" si="3"/>
-        <v>2840669455.6898041</v>
-      </c>
-      <c r="F20" s="84">
-        <f>NPV($J$2,$D$2:D20)</f>
-        <v>698768625.74611974</v>
-      </c>
-      <c r="G20" s="94">
-        <f t="shared" si="1"/>
-        <v>0.76559210794031762</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="81">
-        <v>20</v>
-      </c>
-      <c r="B21" s="83">
-        <f t="shared" si="2"/>
-        <v>-912716600</v>
-      </c>
-      <c r="C21" s="83">
-        <f t="shared" si="4"/>
-        <v>1121238047.5383224</v>
-      </c>
-      <c r="D21" s="87">
-        <f t="shared" si="0"/>
-        <v>208521447.53832245</v>
-      </c>
-      <c r="E21" s="87">
-        <f t="shared" si="3"/>
-        <v>3049190903.2281265</v>
-      </c>
-      <c r="F21" s="84">
-        <f>NPV($J$2,$D$2:D21)</f>
-        <v>728388197.03594232</v>
-      </c>
-      <c r="G21" s="94">
-        <f t="shared" si="1"/>
-        <v>0.79804420894277839</v>
+        <v>0.77250698559499809</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -7808,188 +7837,188 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="56" t="s">
+        <v>273</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1" s="57" t="s">
         <v>274</v>
       </c>
-      <c r="B1" s="105" t="s">
-        <v>278</v>
-      </c>
-      <c r="C1" s="80" t="s">
+      <c r="D1" s="57" t="s">
+        <v>276</v>
+      </c>
+      <c r="E1" s="57" t="s">
         <v>275</v>
       </c>
-      <c r="D1" s="80" t="s">
-        <v>277</v>
-      </c>
-      <c r="E1" s="80" t="s">
-        <v>276</v>
-      </c>
     </row>
     <row r="2" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="81">
+      <c r="A2" s="58">
         <v>0</v>
       </c>
-      <c r="B2" s="106" t="s">
-        <v>286</v>
-      </c>
-      <c r="C2" s="104">
+      <c r="B2" s="80" t="s">
+        <v>284</v>
+      </c>
+      <c r="C2" s="79">
         <v>0</v>
       </c>
-      <c r="D2" s="85">
+      <c r="D2" s="62">
         <v>0</v>
       </c>
-      <c r="E2" s="87">
+      <c r="E2" s="64">
         <f>D2</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="81">
+      <c r="A3" s="58">
         <v>1</v>
       </c>
-      <c r="B3" s="106" t="s">
-        <v>287</v>
-      </c>
-      <c r="C3" s="104">
+      <c r="B3" s="80" t="s">
+        <v>285</v>
+      </c>
+      <c r="C3" s="79">
         <v>0.01</v>
       </c>
-      <c r="D3" s="85">
+      <c r="D3" s="62">
         <f>-C3*'EX+Beneficios'!$B$21</f>
         <v>7402166</v>
       </c>
-      <c r="E3" s="87">
+      <c r="E3" s="64">
         <f>D3</f>
         <v>7402166</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="81">
+      <c r="A4" s="58">
         <v>2</v>
       </c>
-      <c r="B4" s="106" t="s">
-        <v>279</v>
-      </c>
-      <c r="C4" s="104">
+      <c r="B4" s="80" t="s">
+        <v>278</v>
+      </c>
+      <c r="C4" s="79">
         <v>0.15</v>
       </c>
-      <c r="D4" s="85">
+      <c r="D4" s="62">
         <f>-C4*'EX+Beneficios'!$B$21</f>
         <v>111032490</v>
       </c>
-      <c r="E4" s="87">
+      <c r="E4" s="64">
         <f>E3+D4</f>
         <v>118434656</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="81">
+      <c r="A5" s="58">
         <v>3</v>
       </c>
-      <c r="B5" s="106" t="s">
-        <v>285</v>
-      </c>
-      <c r="C5" s="104">
+      <c r="B5" s="80" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" s="79">
         <v>0.5</v>
       </c>
-      <c r="D5" s="85">
+      <c r="D5" s="62">
         <f>-C5*'EX+Beneficios'!$B$21</f>
         <v>370108300</v>
       </c>
-      <c r="E5" s="87">
+      <c r="E5" s="64">
         <f t="shared" ref="E5:E10" si="0">E4+D5</f>
         <v>488542956</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="81">
+      <c r="A6" s="58">
         <v>4</v>
       </c>
-      <c r="B6" s="106" t="s">
-        <v>280</v>
-      </c>
-      <c r="C6" s="104">
+      <c r="B6" s="80" t="s">
+        <v>279</v>
+      </c>
+      <c r="C6" s="79">
         <v>0.1</v>
       </c>
-      <c r="D6" s="85">
+      <c r="D6" s="62">
         <f>-C6*'EX+Beneficios'!$B$21</f>
         <v>74021660</v>
       </c>
-      <c r="E6" s="87">
+      <c r="E6" s="64">
         <f t="shared" si="0"/>
         <v>562564616</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="81">
+      <c r="A7" s="58">
         <v>5</v>
       </c>
-      <c r="B7" s="106" t="s">
-        <v>281</v>
-      </c>
-      <c r="C7" s="104">
+      <c r="B7" s="80" t="s">
+        <v>280</v>
+      </c>
+      <c r="C7" s="79">
         <v>0.08</v>
       </c>
-      <c r="D7" s="85">
+      <c r="D7" s="62">
         <f>-C7*'EX+Beneficios'!$B$21</f>
         <v>59217328</v>
       </c>
-      <c r="E7" s="87">
+      <c r="E7" s="64">
         <f t="shared" si="0"/>
         <v>621781944</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="81">
+      <c r="A8" s="58">
         <v>6</v>
       </c>
-      <c r="B8" s="106" t="s">
-        <v>282</v>
-      </c>
-      <c r="C8" s="104">
+      <c r="B8" s="80" t="s">
+        <v>281</v>
+      </c>
+      <c r="C8" s="79">
         <v>0.1</v>
       </c>
-      <c r="D8" s="85">
+      <c r="D8" s="62">
         <f>-C8*'EX+Beneficios'!$B$21</f>
         <v>74021660</v>
       </c>
-      <c r="E8" s="87">
+      <c r="E8" s="64">
         <f t="shared" si="0"/>
         <v>695803604</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="81">
+      <c r="A9" s="58">
         <v>7</v>
       </c>
-      <c r="B9" s="106" t="s">
-        <v>283</v>
-      </c>
-      <c r="C9" s="104">
+      <c r="B9" s="80" t="s">
+        <v>282</v>
+      </c>
+      <c r="C9" s="79">
         <v>0.04</v>
       </c>
-      <c r="D9" s="85">
+      <c r="D9" s="62">
         <f>-C9*'EX+Beneficios'!$B$21</f>
         <v>29608664</v>
       </c>
-      <c r="E9" s="87">
+      <c r="E9" s="64">
         <f t="shared" si="0"/>
         <v>725412268</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="81">
+      <c r="A10" s="58">
         <v>8</v>
       </c>
-      <c r="B10" s="106" t="s">
-        <v>284</v>
-      </c>
-      <c r="C10" s="104">
+      <c r="B10" s="80" t="s">
+        <v>283</v>
+      </c>
+      <c r="C10" s="79">
         <v>0.02</v>
       </c>
-      <c r="D10" s="85">
+      <c r="D10" s="62">
         <f>-C10*'EX+Beneficios'!$B$21</f>
         <v>14804332</v>
       </c>
-      <c r="E10" s="87">
+      <c r="E10" s="64">
         <f t="shared" si="0"/>
         <v>740216600</v>
       </c>
@@ -7998,7 +8027,7 @@
       <c r="C11" s="14"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C12" s="36"/>
+      <c r="C12" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
